--- a/dane.xlsx
+++ b/dane.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romek_2llxmzw\Documents\Flagi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AC7CE3-76F8-48EF-A4DE-E655AC3CAF60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2498F3-8FD0-4E1B-90D2-6B2F7D41447C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="7545" xr2:uid="{955BB4B8-39B7-4F89-9DFC-9E1092622E04}"/>
   </bookViews>
